--- a/_104_Missions.xlsx
+++ b/_104_Missions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE057CB8-6F2C-4CA9-B31A-0F8E7ADB22DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C35895-0EEF-4292-BE74-677F21038925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7963" yWindow="4217" windowWidth="22114" windowHeight="12969" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="3413" yWindow="2715" windowWidth="21599" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,11 +50,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>reward</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[string]</t>
+    <t>EMissionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kill</t>
+  </si>
+  <si>
+    <t>Kill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WorkCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetIt_ExpCard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[rewardKeys]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[rewardCounts]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,17 +150,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,161 +506,252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:E54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:J54"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="34" width="12.5703125" customWidth="1"/>
+    <col min="1" max="38" width="12.5625" style="4" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>3</v>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="2">
+        <v>1040001</v>
+      </c>
+      <c r="B4" s="2">
+        <v>9030001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1010001</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1010002</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1010003</v>
+      </c>
+      <c r="H4" s="2">
+        <v>200</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J4" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="3">
+        <v>1040002</v>
+      </c>
+      <c r="B5" s="3">
+        <v>9030001</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
+      <c r="D5" s="6">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1010001</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1010003</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1010003</v>
+      </c>
+      <c r="H5" s="3">
+        <v>300</v>
+      </c>
+      <c r="I5" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J5" s="3">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1">
-        <v>1040001</v>
-      </c>
-      <c r="B4" s="1">
-        <v>9030001</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="2">
+        <v>1040003</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9030002</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
         <v>1010001</v>
       </c>
-      <c r="D4" s="1">
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1010003</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="3">
+        <v>1040004</v>
+      </c>
+      <c r="B7" s="3">
+        <v>9030003</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1010001</v>
+      </c>
+      <c r="F7" s="3">
         <v>1010002</v>
       </c>
-      <c r="E4" s="1">
-        <v>0</v>
+      <c r="G7" s="3">
+        <v>1010003</v>
+      </c>
+      <c r="H7" s="3">
+        <v>500</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J7" s="3">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2">
-        <v>1040002</v>
-      </c>
-      <c r="B5" s="2">
-        <v>9030002</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1010001</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1010003</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1">
-        <v>1040003</v>
-      </c>
-      <c r="B6" s="1">
-        <v>9030003</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1010001</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2">
-        <v>1040004</v>
-      </c>
-      <c r="B7" s="2">
-        <v>9030004</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1010001</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1010002</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1010003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="27" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="28" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="32" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="33" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_104_Missions.xlsx
+++ b/_104_Missions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C35895-0EEF-4292-BE74-677F21038925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029A31A0-905D-4A5A-85D3-A8FEB4BA8D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3413" yWindow="2715" windowWidth="21599" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Kill</t>
-  </si>
-  <si>
-    <t>Kill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -86,6 +83,38 @@
   </si>
   <si>
     <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LogIn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LogIn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cycleType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMissionCycleType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weekly</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -150,7 +179,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -165,12 +194,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,14 +529,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:J54"/>
+  <dimension ref="A2:L54"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="38" width="12.5625" style="4" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="4"/>
+    <col min="1" max="3" width="12.5625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="18.5625" style="4" customWidth="1"/>
+    <col min="5" max="40" width="12.5625" style="4" customWidth="1"/>
+    <col min="41" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,31 +546,37 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -556,28 +587,34 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>1040001</v>
       </c>
@@ -585,95 +622,113 @@
         <v>9030001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="5">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
         <v>1010001</v>
       </c>
-      <c r="F4" s="2">
-        <v>1010002</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1010003</v>
-      </c>
       <c r="H4" s="2">
-        <v>200</v>
+        <v>1010001</v>
       </c>
       <c r="I4" s="2">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>1040002</v>
       </c>
       <c r="B5" s="3">
-        <v>9030001</v>
+        <v>9030002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E5" s="3">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3">
         <v>1010001</v>
       </c>
-      <c r="F5" s="3">
-        <v>1010003</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1010003</v>
-      </c>
       <c r="H5" s="3">
-        <v>300</v>
+        <v>1010001</v>
       </c>
       <c r="I5" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3">
-        <v>30</v>
+        <v>500</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>1040003</v>
       </c>
       <c r="B6" s="2">
-        <v>9030002</v>
+        <v>9030003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="5">
-        <v>20</v>
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>1010001</v>
       </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1010003</v>
-      </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>1010002</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>1010004</v>
       </c>
       <c r="J6" s="2">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="K6" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L6" s="2">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>1040004</v>
       </c>
@@ -681,39 +736,119 @@
         <v>9030003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="6">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="3">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1010001</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1010002</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1010004</v>
+      </c>
+      <c r="J7" s="3">
+        <v>300</v>
+      </c>
+      <c r="K7" s="3">
+        <v>30000</v>
+      </c>
+      <c r="L7" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="2">
+        <v>1040005</v>
+      </c>
+      <c r="B8" s="2">
+        <v>9030004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2">
         <v>5</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <v>1010001</v>
       </c>
-      <c r="F7" s="3">
+      <c r="H8" s="2">
         <v>1010002</v>
       </c>
-      <c r="G7" s="3">
-        <v>1010003</v>
-      </c>
-      <c r="H7" s="3">
-        <v>500</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J7" s="3">
-        <v>30</v>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>300</v>
+      </c>
+      <c r="K8" s="2">
+        <v>20000</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="9" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="3">
+        <v>1040006</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9030005</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1010001</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1010002</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1010004</v>
+      </c>
+      <c r="J9" s="3">
+        <v>300</v>
+      </c>
+      <c r="K9" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>

--- a/_104_Missions.xlsx
+++ b/_104_Missions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029A31A0-905D-4A5A-85D3-A8FEB4BA8D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2513C5DF-6CBB-4841-A4D0-5E1ACD8DF0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -637,7 +637,7 @@
         <v>1010001</v>
       </c>
       <c r="H4" s="2">
-        <v>1010001</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>1010001</v>
       </c>
       <c r="H5" s="3">
-        <v>1010001</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
@@ -707,7 +707,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2">
         <v>1010001</v>
@@ -745,7 +745,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G7" s="3">
         <v>1010001</v>
@@ -783,7 +783,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2">
         <v>1010001</v>
@@ -821,7 +821,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3">
         <v>1010001</v>
